--- a/data/output/rda/runs/v9-narrative/evaluation_results.xlsx
+++ b/data/output/rda/runs/v9-narrative/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="289">
   <si>
     <t>fields in reference</t>
   </si>
@@ -233,24 +233,30 @@
     <t>dmp.dataset[2].distribution[0].host.title</t>
   </si>
   <si>
-    <t>dmp.dataset[0].distribution[1].host.title</t>
-  </si>
-  <si>
     <t>dmp.dataset[0].metadata[0].description</t>
   </si>
   <si>
     <t>dmp.dataset[1].metadata[0].description</t>
   </si>
   <si>
+    <t>dmp.dataset[1].metadata[0].language</t>
+  </si>
+  <si>
     <t>dmp.dataset[1].metadata[1].description</t>
   </si>
   <si>
     <t>dmp.dataset[2].distribution[0].license[0].license_ref</t>
   </si>
   <si>
+    <t>dmp.dataset[2].metadata[0].language</t>
+  </si>
+  <si>
     <t>dmp.dataset[3].description</t>
   </si>
   <si>
+    <t>dmp.dataset[3].metadata[0].language</t>
+  </si>
+  <si>
     <t>dmp.description</t>
   </si>
   <si>
@@ -374,9 +380,6 @@
     <t>servers at the Rehabilitation Institute of Chicago</t>
   </si>
   <si>
-    <t>project's website</t>
-  </si>
-  <si>
     <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
   </si>
   <si>
@@ -387,9 +390,6 @@
   </si>
   <si>
     <t>The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>labs' websites</t>
   </si>
   <si>
     <t>GNU Public License</t>
@@ -1301,37 +1301,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>75</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0.307</v>
+        <v>0.387</v>
       </c>
       <c r="H2">
-        <v>0.167</v>
+        <v>0.289</v>
       </c>
       <c r="I2">
-        <v>0.216</v>
+        <v>0.331</v>
       </c>
       <c r="J2">
-        <v>0.23</v>
+        <v>0.2843137254901961</v>
       </c>
       <c r="K2">
-        <v>0.52</v>
+        <v>0.4509803921568628</v>
       </c>
       <c r="L2">
-        <v>0.25</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1339,37 +1339,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>81</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0.333</v>
+        <v>0.407</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="I3">
-        <v>0.25</v>
+        <v>0.356</v>
       </c>
       <c r="J3">
-        <v>0.2571428571428571</v>
+        <v>0.308411214953271</v>
       </c>
       <c r="K3">
-        <v>0.5142857142857142</v>
+        <v>0.4485981308411215</v>
       </c>
       <c r="L3">
-        <v>0.2285714285714286</v>
+        <v>0.2429906542056075</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1377,37 +1377,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>145</v>
       </c>
       <c r="D4">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E4">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0.428</v>
+        <v>0.469</v>
       </c>
       <c r="H4">
-        <v>0.333</v>
+        <v>0.421</v>
       </c>
       <c r="I4">
-        <v>0.375</v>
+        <v>0.444</v>
       </c>
       <c r="J4">
-        <v>0.3757575757575757</v>
+        <v>0.407185628742515</v>
       </c>
       <c r="K4">
-        <v>0.503030303030303</v>
+        <v>0.4610778443113773</v>
       </c>
       <c r="L4">
-        <v>0.1212121212121212</v>
+        <v>0.1317365269461078</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1522,7 +1522,7 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
         <v>129</v>
@@ -1542,7 +1542,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
         <v>129</v>
@@ -1562,7 +1562,7 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F8" t="s">
         <v>129</v>
@@ -1582,7 +1582,7 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
         <v>129</v>
@@ -1602,7 +1602,7 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
         <v>129</v>
@@ -1622,10 +1622,10 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
         <v>129</v>
@@ -1645,7 +1645,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
         <v>129</v>
@@ -1665,7 +1665,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
         <v>129</v>
@@ -1685,7 +1685,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>129</v>
@@ -1705,7 +1705,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
         <v>129</v>
@@ -1725,7 +1725,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
         <v>129</v>
@@ -1745,10 +1745,10 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
         <v>129</v>
@@ -1768,7 +1768,7 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
         <v>129</v>
@@ -1788,7 +1788,7 @@
         <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
         <v>129</v>
@@ -1808,7 +1808,7 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
         <v>129</v>
@@ -1828,7 +1828,7 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
         <v>129</v>
@@ -1848,7 +1848,7 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
         <v>129</v>
@@ -1868,10 +1868,10 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
         <v>129</v>
@@ -1891,7 +1891,7 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
         <v>129</v>
@@ -1911,7 +1911,7 @@
         <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
         <v>129</v>
@@ -1931,7 +1931,7 @@
         <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
         <v>129</v>
@@ -1951,7 +1951,7 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
         <v>129</v>
@@ -1971,7 +1971,7 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
         <v>129</v>
@@ -1991,7 +1991,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
         <v>129</v>
@@ -2011,7 +2011,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s">
         <v>129</v>
@@ -2031,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s">
         <v>129</v>
@@ -2051,7 +2051,7 @@
         <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s">
         <v>129</v>
@@ -2071,7 +2071,7 @@
         <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
         <v>129</v>
@@ -2091,7 +2091,7 @@
         <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
         <v>129</v>
@@ -2111,7 +2111,7 @@
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
         <v>129</v>
@@ -2131,10 +2131,10 @@
         <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F36" t="s">
         <v>128</v>
@@ -2151,7 +2151,7 @@
         <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F37" t="s">
         <v>129</v>
@@ -2171,7 +2171,7 @@
         <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
         <v>129</v>
@@ -2191,7 +2191,7 @@
         <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F39" t="s">
         <v>129</v>
@@ -2211,7 +2211,7 @@
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F40" t="s">
         <v>129</v>
@@ -2231,7 +2231,7 @@
         <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
         <v>129</v>
@@ -2251,7 +2251,7 @@
         <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
         <v>129</v>
@@ -2268,7 +2268,7 @@
         <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F43" t="s">
         <v>130</v>
@@ -2282,7 +2282,7 @@
         <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
         <v>130</v>
@@ -2296,7 +2296,7 @@
         <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F45" t="s">
         <v>130</v>
@@ -2310,7 +2310,7 @@
         <v>65</v>
       </c>
       <c r="E46" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F46" t="s">
         <v>130</v>
@@ -2324,7 +2324,7 @@
         <v>66</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F47" t="s">
         <v>130</v>
@@ -2338,7 +2338,7 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F48" t="s">
         <v>130</v>
@@ -2352,7 +2352,7 @@
         <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F49" t="s">
         <v>130</v>
@@ -2366,7 +2366,7 @@
         <v>37</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F50" t="s">
         <v>130</v>
@@ -2380,7 +2380,7 @@
         <v>69</v>
       </c>
       <c r="E51" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
@@ -2394,7 +2394,7 @@
         <v>70</v>
       </c>
       <c r="E52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F52" t="s">
         <v>130</v>
@@ -2408,7 +2408,7 @@
         <v>43</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F53" t="s">
         <v>130</v>
@@ -2493,7 +2493,7 @@
         <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F58" t="s">
         <v>129</v>
@@ -2547,13 +2547,13 @@
         <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E61" t="s">
+        <v>83</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
-      </c>
-      <c r="G61" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2567,13 +2567,13 @@
         <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E62" t="s">
+        <v>83</v>
       </c>
       <c r="F62" t="s">
-        <v>129</v>
-      </c>
-      <c r="G62" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2587,10 +2587,10 @@
         <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F63" t="s">
         <v>128</v>
@@ -2607,7 +2607,7 @@
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F64" t="s">
         <v>129</v>
@@ -2661,13 +2661,13 @@
         <v>35</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E67" t="s">
+        <v>83</v>
       </c>
       <c r="F67" t="s">
-        <v>129</v>
-      </c>
-      <c r="G67" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2681,13 +2681,13 @@
         <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E68" t="s">
+        <v>83</v>
       </c>
       <c r="F68" t="s">
-        <v>129</v>
-      </c>
-      <c r="G68" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>37</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F69" t="s">
         <v>128</v>
@@ -2721,7 +2721,7 @@
         <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F70" t="s">
         <v>129</v>
@@ -2775,13 +2775,13 @@
         <v>41</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E73" t="s">
+        <v>83</v>
       </c>
       <c r="F73" t="s">
-        <v>129</v>
-      </c>
-      <c r="G73" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2795,13 +2795,13 @@
         <v>42</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E74" t="s">
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>129</v>
-      </c>
-      <c r="G74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2815,10 +2815,10 @@
         <v>43</v>
       </c>
       <c r="D75" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E75" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F75" t="s">
         <v>128</v>
@@ -2835,7 +2835,7 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F76" t="s">
         <v>129</v>
@@ -2889,7 +2889,7 @@
         <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F79" t="s">
         <v>129</v>
@@ -2909,7 +2909,7 @@
         <v>54</v>
       </c>
       <c r="D80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F80" t="s">
         <v>129</v>
@@ -2929,7 +2929,7 @@
         <v>55</v>
       </c>
       <c r="D81" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F81" t="s">
         <v>129</v>
@@ -2949,10 +2949,10 @@
         <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E82" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F82" t="s">
         <v>128</v>
@@ -2969,7 +2969,7 @@
         <v>57</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F83" t="s">
         <v>129</v>
@@ -2989,7 +2989,7 @@
         <v>58</v>
       </c>
       <c r="D84" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F84" t="s">
         <v>129</v>
@@ -3043,7 +3043,7 @@
         <v>62</v>
       </c>
       <c r="D87" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F87" t="s">
         <v>129</v>
@@ -3060,7 +3060,7 @@
         <v>63</v>
       </c>
       <c r="E88" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F88" t="s">
         <v>130</v>
@@ -3074,7 +3074,7 @@
         <v>64</v>
       </c>
       <c r="E89" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
         <v>130</v>
@@ -3088,7 +3088,7 @@
         <v>71</v>
       </c>
       <c r="E90" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F90" t="s">
         <v>130</v>
@@ -3099,10 +3099,10 @@
         <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F91" t="s">
         <v>130</v>
@@ -3113,7 +3113,7 @@
         <v>3</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E92" t="s">
         <v>120</v>
@@ -3127,10 +3127,10 @@
         <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E93" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F93" t="s">
         <v>130</v>
@@ -3141,10 +3141,10 @@
         <v>3</v>
       </c>
       <c r="B94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E94" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F94" t="s">
         <v>130</v>
@@ -3155,10 +3155,10 @@
         <v>3</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E95" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F95" t="s">
         <v>130</v>
@@ -3169,10 +3169,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E96" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
         <v>130</v>
@@ -3183,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E97" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="F97" t="s">
         <v>130</v>
@@ -3197,10 +3197,10 @@
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F98" t="s">
         <v>130</v>
@@ -3211,10 +3211,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="F99" t="s">
         <v>130</v>
@@ -3225,10 +3225,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E100" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F100" t="s">
         <v>130</v>
@@ -3239,12 +3239,40 @@
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E101" t="s">
+        <v>83</v>
+      </c>
+      <c r="F101" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>3</v>
+      </c>
+      <c r="B102" t="s">
+        <v>49</v>
+      </c>
+      <c r="E102" t="s">
+        <v>126</v>
+      </c>
+      <c r="F102" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103">
+        <v>3</v>
+      </c>
+      <c r="B103" t="s">
+        <v>79</v>
+      </c>
+      <c r="E103" t="s">
         <v>127</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F103" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3255,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3463,7 +3491,7 @@
         <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
         <v>129</v>
@@ -3486,7 +3514,7 @@
         <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
         <v>129</v>
@@ -3566,10 +3594,10 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
         <v>128</v>
@@ -3820,7 +3848,7 @@
         <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
         <v>129</v>
@@ -3871,10 +3899,10 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
         <v>176</v>
@@ -4054,7 +4082,7 @@
         <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F41" t="s">
         <v>129</v>
@@ -4094,10 +4122,10 @@
         <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F43" t="s">
         <v>128</v>
@@ -4242,7 +4270,7 @@
         <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
@@ -4256,7 +4284,7 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F52" t="s">
         <v>130</v>
@@ -4270,7 +4298,7 @@
         <v>65</v>
       </c>
       <c r="E53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F53" t="s">
         <v>130</v>
@@ -4284,7 +4312,7 @@
         <v>66</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s">
         <v>130</v>
@@ -4298,7 +4326,7 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
         <v>130</v>
@@ -4312,7 +4340,7 @@
         <v>68</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F56" t="s">
         <v>130</v>
@@ -4326,7 +4354,7 @@
         <v>37</v>
       </c>
       <c r="E57" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F57" t="s">
         <v>130</v>
@@ -4340,7 +4368,7 @@
         <v>69</v>
       </c>
       <c r="E58" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F58" t="s">
         <v>130</v>
@@ -4354,7 +4382,7 @@
         <v>70</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>130</v>
@@ -4368,7 +4396,7 @@
         <v>43</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F60" t="s">
         <v>130</v>
@@ -4513,13 +4541,13 @@
         <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E68" t="s">
+        <v>83</v>
       </c>
       <c r="F68" t="s">
-        <v>129</v>
-      </c>
-      <c r="G68" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4533,13 +4561,13 @@
         <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E69" t="s">
+        <v>83</v>
       </c>
       <c r="F69" t="s">
-        <v>129</v>
-      </c>
-      <c r="G69" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4553,10 +4581,10 @@
         <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E70" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F70" t="s">
         <v>128</v>
@@ -4576,7 +4604,7 @@
         <v>182</v>
       </c>
       <c r="E71" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F71" t="s">
         <v>128</v>
@@ -4630,13 +4658,13 @@
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E74" t="s">
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>129</v>
-      </c>
-      <c r="G74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4650,13 +4678,13 @@
         <v>36</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E75" t="s">
+        <v>83</v>
       </c>
       <c r="F75" t="s">
-        <v>129</v>
-      </c>
-      <c r="G75" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4670,10 +4698,10 @@
         <v>37</v>
       </c>
       <c r="D76" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F76" t="s">
         <v>128</v>
@@ -4693,7 +4721,7 @@
         <v>183</v>
       </c>
       <c r="E77" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F77" t="s">
         <v>129</v>
@@ -4750,13 +4778,13 @@
         <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E80" t="s">
+        <v>83</v>
       </c>
       <c r="F80" t="s">
-        <v>129</v>
-      </c>
-      <c r="G80" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4770,13 +4798,13 @@
         <v>42</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E81" t="s">
+        <v>83</v>
       </c>
       <c r="F81" t="s">
-        <v>129</v>
-      </c>
-      <c r="G81" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4793,7 +4821,7 @@
         <v>184</v>
       </c>
       <c r="E82" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F82" t="s">
         <v>129</v>
@@ -4816,7 +4844,7 @@
         <v>185</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F83" t="s">
         <v>129</v>
@@ -4873,7 +4901,7 @@
         <v>53</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F86" t="s">
         <v>129</v>
@@ -4893,7 +4921,7 @@
         <v>54</v>
       </c>
       <c r="D87" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F87" t="s">
         <v>129</v>
@@ -4933,10 +4961,10 @@
         <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E89" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F89" t="s">
         <v>128</v>
@@ -5001,7 +5029,7 @@
         <v>64</v>
       </c>
       <c r="E93" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
         <v>130</v>
@@ -5015,7 +5043,7 @@
         <v>71</v>
       </c>
       <c r="E94" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F94" t="s">
         <v>130</v>
@@ -5026,10 +5054,10 @@
         <v>3</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E95" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F95" t="s">
         <v>130</v>
@@ -5040,7 +5068,7 @@
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E96" t="s">
         <v>120</v>
@@ -5054,10 +5082,10 @@
         <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E97" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F97" t="s">
         <v>130</v>
@@ -5068,10 +5096,10 @@
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E98" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F98" t="s">
         <v>130</v>
@@ -5082,10 +5110,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E99" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F99" t="s">
         <v>130</v>
@@ -5096,10 +5124,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F100" t="s">
         <v>130</v>
@@ -5110,10 +5138,10 @@
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E101" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="F101" t="s">
         <v>130</v>
@@ -5124,10 +5152,10 @@
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F102" t="s">
         <v>130</v>
@@ -5138,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="E103" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F103" t="s">
         <v>130</v>
@@ -5152,10 +5180,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E104" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="F104" t="s">
         <v>130</v>
@@ -5166,10 +5194,10 @@
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E105" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F105" t="s">
         <v>130</v>
@@ -5180,12 +5208,40 @@
         <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E106" t="s">
+        <v>83</v>
+      </c>
+      <c r="F106" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107">
+        <v>3</v>
+      </c>
+      <c r="B107" t="s">
+        <v>49</v>
+      </c>
+      <c r="E107" t="s">
+        <v>126</v>
+      </c>
+      <c r="F107" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108">
+        <v>3</v>
+      </c>
+      <c r="B108" t="s">
+        <v>79</v>
+      </c>
+      <c r="E108" t="s">
         <v>127</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F108" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5196,7 +5252,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5398,7 +5454,7 @@
         <v>256</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
         <v>129</v>
@@ -5421,7 +5477,7 @@
         <v>257</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
         <v>129</v>
@@ -5461,7 +5517,7 @@
         <v>136</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
         <v>129</v>
@@ -5484,7 +5540,7 @@
         <v>258</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
         <v>128</v>
@@ -5632,7 +5688,7 @@
         <v>260</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
         <v>129</v>
@@ -5655,7 +5711,7 @@
         <v>261</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s">
         <v>129</v>
@@ -5695,7 +5751,7 @@
         <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
         <v>129</v>
@@ -5718,7 +5774,7 @@
         <v>258</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
         <v>128</v>
@@ -5866,7 +5922,7 @@
         <v>262</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
         <v>129</v>
@@ -5889,7 +5945,7 @@
         <v>263</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F36" t="s">
         <v>129</v>
@@ -5929,7 +5985,7 @@
         <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
         <v>129</v>
@@ -5952,7 +6008,7 @@
         <v>258</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
         <v>128</v>
@@ -6111,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
         <v>265</v>
@@ -7226,7 +7282,7 @@
         <v>54</v>
       </c>
       <c r="D106" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F106" t="s">
         <v>129</v>
@@ -7266,10 +7322,10 @@
         <v>56</v>
       </c>
       <c r="D108" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E108" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F108" t="s">
         <v>128</v>
@@ -7283,7 +7339,7 @@
         <v>63</v>
       </c>
       <c r="E109" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F109" t="s">
         <v>130</v>
@@ -7297,7 +7353,7 @@
         <v>31</v>
       </c>
       <c r="E110" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F110" t="s">
         <v>130</v>
@@ -7311,7 +7367,7 @@
         <v>65</v>
       </c>
       <c r="E111" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F111" t="s">
         <v>130</v>
@@ -7325,7 +7381,7 @@
         <v>67</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F112" t="s">
         <v>130</v>
@@ -7339,7 +7395,7 @@
         <v>68</v>
       </c>
       <c r="E113" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F113" t="s">
         <v>130</v>
@@ -7353,7 +7409,7 @@
         <v>37</v>
       </c>
       <c r="E114" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F114" t="s">
         <v>130</v>
@@ -7367,7 +7423,7 @@
         <v>69</v>
       </c>
       <c r="E115" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F115" t="s">
         <v>130</v>
@@ -7381,7 +7437,7 @@
         <v>43</v>
       </c>
       <c r="E116" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F116" t="s">
         <v>130</v>
@@ -7520,13 +7576,13 @@
         <v>29</v>
       </c>
       <c r="D124" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E124" t="s">
+        <v>83</v>
       </c>
       <c r="F124" t="s">
-        <v>129</v>
-      </c>
-      <c r="G124" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -7540,13 +7596,13 @@
         <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E125" t="s">
+        <v>83</v>
       </c>
       <c r="F125" t="s">
-        <v>129</v>
-      </c>
-      <c r="G125" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -7563,7 +7619,7 @@
         <v>280</v>
       </c>
       <c r="E126" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F126" t="s">
         <v>129</v>
@@ -7586,7 +7642,7 @@
         <v>281</v>
       </c>
       <c r="E127" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F127" t="s">
         <v>128</v>
@@ -7637,13 +7693,13 @@
         <v>35</v>
       </c>
       <c r="D130" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E130" t="s">
+        <v>83</v>
       </c>
       <c r="F130" t="s">
-        <v>129</v>
-      </c>
-      <c r="G130" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -7657,13 +7713,13 @@
         <v>36</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E131" t="s">
+        <v>83</v>
       </c>
       <c r="F131" t="s">
-        <v>129</v>
-      </c>
-      <c r="G131" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7680,7 +7736,7 @@
         <v>282</v>
       </c>
       <c r="E132" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F132" t="s">
         <v>128</v>
@@ -7700,7 +7756,7 @@
         <v>283</v>
       </c>
       <c r="E133" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F133" t="s">
         <v>128</v>
@@ -7751,13 +7807,13 @@
         <v>41</v>
       </c>
       <c r="D136" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E136" t="s">
+        <v>83</v>
       </c>
       <c r="F136" t="s">
-        <v>129</v>
-      </c>
-      <c r="G136" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7771,13 +7827,13 @@
         <v>42</v>
       </c>
       <c r="D137" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E137" t="s">
+        <v>83</v>
       </c>
       <c r="F137" t="s">
-        <v>129</v>
-      </c>
-      <c r="G137" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7794,7 +7850,7 @@
         <v>284</v>
       </c>
       <c r="E138" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F138" t="s">
         <v>128</v>
@@ -7811,10 +7867,10 @@
         <v>69</v>
       </c>
       <c r="D139" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E139" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F139" t="s">
         <v>128</v>
@@ -7865,7 +7921,7 @@
         <v>53</v>
       </c>
       <c r="D142" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F142" t="s">
         <v>129</v>
@@ -7885,7 +7941,7 @@
         <v>54</v>
       </c>
       <c r="D143" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F143" t="s">
         <v>129</v>
@@ -7925,10 +7981,10 @@
         <v>56</v>
       </c>
       <c r="D145" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E145" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F145" t="s">
         <v>128</v>
@@ -7939,10 +7995,10 @@
         <v>3</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D146" t="s">
         <v>285</v>
@@ -7968,7 +8024,7 @@
         <v>57</v>
       </c>
       <c r="D147" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F147" t="s">
         <v>129</v>
@@ -7988,7 +8044,7 @@
         <v>58</v>
       </c>
       <c r="D148" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F148" t="s">
         <v>129</v>
@@ -8110,7 +8166,7 @@
         <v>64</v>
       </c>
       <c r="E155" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F155" t="s">
         <v>130</v>
@@ -8124,7 +8180,7 @@
         <v>71</v>
       </c>
       <c r="E156" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F156" t="s">
         <v>130</v>
@@ -8135,10 +8191,10 @@
         <v>3</v>
       </c>
       <c r="B157" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E157" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F157" t="s">
         <v>130</v>
@@ -8149,10 +8205,10 @@
         <v>3</v>
       </c>
       <c r="B158" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E158" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F158" t="s">
         <v>130</v>
@@ -8163,10 +8219,10 @@
         <v>3</v>
       </c>
       <c r="B159" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E159" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F159" t="s">
         <v>130</v>
@@ -8177,10 +8233,10 @@
         <v>3</v>
       </c>
       <c r="B160" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E160" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F160" t="s">
         <v>130</v>
@@ -8191,10 +8247,10 @@
         <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E161" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F161" t="s">
         <v>130</v>
@@ -8205,10 +8261,10 @@
         <v>3</v>
       </c>
       <c r="B162" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E162" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="F162" t="s">
         <v>130</v>
@@ -8219,10 +8275,10 @@
         <v>3</v>
       </c>
       <c r="B163" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E163" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F163" t="s">
         <v>130</v>
@@ -8233,10 +8289,10 @@
         <v>3</v>
       </c>
       <c r="B164" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E164" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="F164" t="s">
         <v>130</v>
@@ -8247,10 +8303,10 @@
         <v>3</v>
       </c>
       <c r="B165" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E165" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F165" t="s">
         <v>130</v>
@@ -8261,12 +8317,40 @@
         <v>3</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E166" t="s">
+        <v>83</v>
+      </c>
+      <c r="F166" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167">
+        <v>3</v>
+      </c>
+      <c r="B167" t="s">
+        <v>49</v>
+      </c>
+      <c r="E167" t="s">
+        <v>126</v>
+      </c>
+      <c r="F167" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168">
+        <v>3</v>
+      </c>
+      <c r="B168" t="s">
+        <v>79</v>
+      </c>
+      <c r="E168" t="s">
         <v>127</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F168" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8280,7 +8364,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H377"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8403,7 +8487,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s">
         <v>129</v>
@@ -8426,7 +8510,7 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s">
         <v>129</v>
@@ -8449,7 +8533,7 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
         <v>129</v>
@@ -8472,7 +8556,7 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s">
         <v>129</v>
@@ -8495,7 +8579,7 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
@@ -8518,10 +8602,10 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
         <v>129</v>
@@ -8544,7 +8628,7 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
         <v>129</v>
@@ -8567,7 +8651,7 @@
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
         <v>129</v>
@@ -8590,7 +8674,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
         <v>129</v>
@@ -8613,7 +8697,7 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s">
         <v>129</v>
@@ -8636,7 +8720,7 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>129</v>
@@ -8659,10 +8743,10 @@
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G17" t="s">
         <v>129</v>
@@ -8685,7 +8769,7 @@
         <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
         <v>129</v>
@@ -8708,7 +8792,7 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
         <v>129</v>
@@ -8731,7 +8815,7 @@
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
         <v>129</v>
@@ -8754,7 +8838,7 @@
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s">
         <v>129</v>
@@ -8777,7 +8861,7 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s">
         <v>129</v>
@@ -8800,10 +8884,10 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G23" t="s">
         <v>129</v>
@@ -8826,7 +8910,7 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s">
         <v>129</v>
@@ -8849,7 +8933,7 @@
         <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
         <v>129</v>
@@ -8872,7 +8956,7 @@
         <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
         <v>129</v>
@@ -8895,7 +8979,7 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
         <v>129</v>
@@ -8918,7 +9002,7 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s">
         <v>129</v>
@@ -8941,7 +9025,7 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
         <v>129</v>
@@ -8964,7 +9048,7 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s">
         <v>129</v>
@@ -8987,7 +9071,7 @@
         <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
         <v>129</v>
@@ -9010,7 +9094,7 @@
         <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
         <v>129</v>
@@ -9033,7 +9117,7 @@
         <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
         <v>129</v>
@@ -9056,7 +9140,7 @@
         <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s">
         <v>129</v>
@@ -9079,7 +9163,7 @@
         <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
         <v>129</v>
@@ -9102,10 +9186,10 @@
         <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G36" t="s">
         <v>128</v>
@@ -9125,7 +9209,7 @@
         <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
         <v>129</v>
@@ -9148,7 +9232,7 @@
         <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s">
         <v>129</v>
@@ -9171,7 +9255,7 @@
         <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s">
         <v>129</v>
@@ -9194,7 +9278,7 @@
         <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s">
         <v>129</v>
@@ -9217,7 +9301,7 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G41" t="s">
         <v>129</v>
@@ -9240,7 +9324,7 @@
         <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G42" t="s">
         <v>129</v>
@@ -9260,7 +9344,7 @@
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G43" t="s">
         <v>130</v>
@@ -9277,7 +9361,7 @@
         <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G44" t="s">
         <v>130</v>
@@ -9294,7 +9378,7 @@
         <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
         <v>130</v>
@@ -9311,7 +9395,7 @@
         <v>65</v>
       </c>
       <c r="F46" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G46" t="s">
         <v>130</v>
@@ -9328,7 +9412,7 @@
         <v>66</v>
       </c>
       <c r="F47" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G47" t="s">
         <v>130</v>
@@ -9345,7 +9429,7 @@
         <v>67</v>
       </c>
       <c r="F48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G48" t="s">
         <v>130</v>
@@ -9362,7 +9446,7 @@
         <v>68</v>
       </c>
       <c r="F49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G49" t="s">
         <v>130</v>
@@ -9379,7 +9463,7 @@
         <v>37</v>
       </c>
       <c r="F50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
         <v>130</v>
@@ -9396,7 +9480,7 @@
         <v>69</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G51" t="s">
         <v>130</v>
@@ -9413,7 +9497,7 @@
         <v>70</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G52" t="s">
         <v>130</v>
@@ -9430,7 +9514,7 @@
         <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G53" t="s">
         <v>130</v>
@@ -9648,7 +9732,7 @@
         <v>163</v>
       </c>
       <c r="F63" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G63" t="s">
         <v>129</v>
@@ -9674,7 +9758,7 @@
         <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G64" t="s">
         <v>129</v>
@@ -9766,10 +9850,10 @@
         <v>64</v>
       </c>
       <c r="E68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G68" t="s">
         <v>128</v>
@@ -10059,7 +10143,7 @@
         <v>150</v>
       </c>
       <c r="E81" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G81" t="s">
         <v>129</v>
@@ -10119,10 +10203,10 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E84" t="s">
         <v>176</v>
@@ -10329,7 +10413,7 @@
         <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G93" t="s">
         <v>129</v>
@@ -10375,10 +10459,10 @@
         <v>56</v>
       </c>
       <c r="E95" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F95" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G95" t="s">
         <v>128</v>
@@ -10547,7 +10631,7 @@
         <v>63</v>
       </c>
       <c r="F103" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G103" t="s">
         <v>130</v>
@@ -10564,7 +10648,7 @@
         <v>31</v>
       </c>
       <c r="F104" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G104" t="s">
         <v>130</v>
@@ -10581,7 +10665,7 @@
         <v>65</v>
       </c>
       <c r="F105" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G105" t="s">
         <v>130</v>
@@ -10598,7 +10682,7 @@
         <v>66</v>
       </c>
       <c r="F106" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G106" t="s">
         <v>130</v>
@@ -10615,7 +10699,7 @@
         <v>67</v>
       </c>
       <c r="F107" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G107" t="s">
         <v>130</v>
@@ -10632,7 +10716,7 @@
         <v>68</v>
       </c>
       <c r="F108" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G108" t="s">
         <v>130</v>
@@ -10649,7 +10733,7 @@
         <v>37</v>
       </c>
       <c r="F109" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G109" t="s">
         <v>130</v>
@@ -10666,7 +10750,7 @@
         <v>69</v>
       </c>
       <c r="F110" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G110" t="s">
         <v>130</v>
@@ -10683,7 +10767,7 @@
         <v>70</v>
       </c>
       <c r="F111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G111" t="s">
         <v>130</v>
@@ -10700,7 +10784,7 @@
         <v>43</v>
       </c>
       <c r="F112" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G112" t="s">
         <v>130</v>
@@ -10912,7 +10996,7 @@
         <v>256</v>
       </c>
       <c r="F122" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G122" t="s">
         <v>129</v>
@@ -10938,7 +11022,7 @@
         <v>257</v>
       </c>
       <c r="F123" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G123" t="s">
         <v>129</v>
@@ -10984,7 +11068,7 @@
         <v>136</v>
       </c>
       <c r="E125" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G125" t="s">
         <v>129</v>
@@ -11010,7 +11094,7 @@
         <v>258</v>
       </c>
       <c r="F126" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G126" t="s">
         <v>128</v>
@@ -11182,7 +11266,7 @@
         <v>260</v>
       </c>
       <c r="F134" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G134" t="s">
         <v>129</v>
@@ -11208,7 +11292,7 @@
         <v>261</v>
       </c>
       <c r="F135" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G135" t="s">
         <v>129</v>
@@ -11254,7 +11338,7 @@
         <v>190</v>
       </c>
       <c r="E137" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G137" t="s">
         <v>129</v>
@@ -11280,7 +11364,7 @@
         <v>258</v>
       </c>
       <c r="F138" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G138" t="s">
         <v>128</v>
@@ -11452,7 +11536,7 @@
         <v>262</v>
       </c>
       <c r="F146" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G146" t="s">
         <v>129</v>
@@ -11478,7 +11562,7 @@
         <v>263</v>
       </c>
       <c r="F147" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G147" t="s">
         <v>129</v>
@@ -11524,7 +11608,7 @@
         <v>195</v>
       </c>
       <c r="E149" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G149" t="s">
         <v>129</v>
@@ -11550,7 +11634,7 @@
         <v>258</v>
       </c>
       <c r="F150" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G150" t="s">
         <v>128</v>
@@ -11736,10 +11820,10 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D159" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E159" t="s">
         <v>265</v>
@@ -13025,7 +13109,7 @@
         <v>54</v>
       </c>
       <c r="E217" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G217" t="s">
         <v>129</v>
@@ -13071,10 +13155,10 @@
         <v>56</v>
       </c>
       <c r="E219" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F219" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G219" t="s">
         <v>128</v>
@@ -13091,7 +13175,7 @@
         <v>63</v>
       </c>
       <c r="F220" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G220" t="s">
         <v>130</v>
@@ -13108,7 +13192,7 @@
         <v>31</v>
       </c>
       <c r="F221" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G221" t="s">
         <v>130</v>
@@ -13125,7 +13209,7 @@
         <v>65</v>
       </c>
       <c r="F222" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G222" t="s">
         <v>130</v>
@@ -13142,7 +13226,7 @@
         <v>67</v>
       </c>
       <c r="F223" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G223" t="s">
         <v>130</v>
@@ -13159,7 +13243,7 @@
         <v>68</v>
       </c>
       <c r="F224" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G224" t="s">
         <v>130</v>
@@ -13176,7 +13260,7 @@
         <v>37</v>
       </c>
       <c r="F225" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G225" t="s">
         <v>130</v>
@@ -13193,7 +13277,7 @@
         <v>69</v>
       </c>
       <c r="F226" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G226" t="s">
         <v>130</v>
@@ -13210,7 +13294,7 @@
         <v>43</v>
       </c>
       <c r="F227" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G227" t="s">
         <v>130</v>
@@ -13310,7 +13394,7 @@
         <v>26</v>
       </c>
       <c r="E232" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G232" t="s">
         <v>129</v>
@@ -13373,13 +13457,13 @@
         <v>29</v>
       </c>
       <c r="E235" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F235" t="s">
+        <v>83</v>
       </c>
       <c r="G235" t="s">
-        <v>129</v>
-      </c>
-      <c r="H235" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -13396,13 +13480,13 @@
         <v>30</v>
       </c>
       <c r="E236" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F236" t="s">
+        <v>83</v>
       </c>
       <c r="G236" t="s">
-        <v>129</v>
-      </c>
-      <c r="H236" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -13419,10 +13503,10 @@
         <v>31</v>
       </c>
       <c r="E237" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F237" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G237" t="s">
         <v>128</v>
@@ -13442,7 +13526,7 @@
         <v>32</v>
       </c>
       <c r="E238" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G238" t="s">
         <v>129</v>
@@ -13505,13 +13589,13 @@
         <v>35</v>
       </c>
       <c r="E241" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F241" t="s">
+        <v>83</v>
       </c>
       <c r="G241" t="s">
-        <v>129</v>
-      </c>
-      <c r="H241" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -13528,13 +13612,13 @@
         <v>36</v>
       </c>
       <c r="E242" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F242" t="s">
+        <v>83</v>
       </c>
       <c r="G242" t="s">
-        <v>129</v>
-      </c>
-      <c r="H242" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -13551,10 +13635,10 @@
         <v>37</v>
       </c>
       <c r="E243" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F243" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G243" t="s">
         <v>128</v>
@@ -13574,7 +13658,7 @@
         <v>38</v>
       </c>
       <c r="E244" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G244" t="s">
         <v>129</v>
@@ -13637,13 +13721,13 @@
         <v>41</v>
       </c>
       <c r="E247" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F247" t="s">
+        <v>83</v>
       </c>
       <c r="G247" t="s">
-        <v>129</v>
-      </c>
-      <c r="H247" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -13660,13 +13744,13 @@
         <v>42</v>
       </c>
       <c r="E248" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F248" t="s">
+        <v>83</v>
       </c>
       <c r="G248" t="s">
-        <v>129</v>
-      </c>
-      <c r="H248" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -13683,10 +13767,10 @@
         <v>43</v>
       </c>
       <c r="E249" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F249" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G249" t="s">
         <v>128</v>
@@ -13706,7 +13790,7 @@
         <v>44</v>
       </c>
       <c r="E250" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G250" t="s">
         <v>129</v>
@@ -13769,7 +13853,7 @@
         <v>53</v>
       </c>
       <c r="E253" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G253" t="s">
         <v>129</v>
@@ -13792,7 +13876,7 @@
         <v>54</v>
       </c>
       <c r="E254" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G254" t="s">
         <v>129</v>
@@ -13815,7 +13899,7 @@
         <v>55</v>
       </c>
       <c r="E255" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G255" t="s">
         <v>129</v>
@@ -13838,10 +13922,10 @@
         <v>56</v>
       </c>
       <c r="E256" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F256" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G256" t="s">
         <v>128</v>
@@ -13861,7 +13945,7 @@
         <v>57</v>
       </c>
       <c r="E257" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G257" t="s">
         <v>129</v>
@@ -13884,7 +13968,7 @@
         <v>58</v>
       </c>
       <c r="E258" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G258" t="s">
         <v>129</v>
@@ -13947,7 +14031,7 @@
         <v>62</v>
       </c>
       <c r="E261" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G261" t="s">
         <v>129</v>
@@ -13967,7 +14051,7 @@
         <v>63</v>
       </c>
       <c r="F262" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G262" t="s">
         <v>130</v>
@@ -13984,7 +14068,7 @@
         <v>64</v>
       </c>
       <c r="F263" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G263" t="s">
         <v>130</v>
@@ -14001,7 +14085,7 @@
         <v>71</v>
       </c>
       <c r="F264" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G264" t="s">
         <v>130</v>
@@ -14015,10 +14099,10 @@
         <v>12</v>
       </c>
       <c r="C265" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F265" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G265" t="s">
         <v>130</v>
@@ -14032,7 +14116,7 @@
         <v>12</v>
       </c>
       <c r="C266" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F266" t="s">
         <v>120</v>
@@ -14049,10 +14133,10 @@
         <v>12</v>
       </c>
       <c r="C267" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F267" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="G267" t="s">
         <v>130</v>
@@ -14066,10 +14150,10 @@
         <v>12</v>
       </c>
       <c r="C268" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F268" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G268" t="s">
         <v>130</v>
@@ -14083,10 +14167,10 @@
         <v>12</v>
       </c>
       <c r="C269" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F269" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G269" t="s">
         <v>130</v>
@@ -14100,10 +14184,10 @@
         <v>12</v>
       </c>
       <c r="C270" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F270" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G270" t="s">
         <v>130</v>
@@ -14117,10 +14201,10 @@
         <v>12</v>
       </c>
       <c r="C271" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F271" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="G271" t="s">
         <v>130</v>
@@ -14134,10 +14218,10 @@
         <v>12</v>
       </c>
       <c r="C272" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F272" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G272" t="s">
         <v>130</v>
@@ -14151,10 +14235,10 @@
         <v>12</v>
       </c>
       <c r="C273" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F273" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="G273" t="s">
         <v>130</v>
@@ -14168,10 +14252,10 @@
         <v>12</v>
       </c>
       <c r="C274" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F274" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="G274" t="s">
         <v>130</v>
@@ -14185,10 +14269,10 @@
         <v>12</v>
       </c>
       <c r="C275" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F275" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="G275" t="s">
         <v>130</v>
@@ -14199,19 +14283,16 @@
         <v>3</v>
       </c>
       <c r="B276" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C276" t="s">
-        <v>22</v>
-      </c>
-      <c r="D276" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="F276" t="s">
+        <v>126</v>
       </c>
       <c r="G276" t="s">
-        <v>128</v>
-      </c>
-      <c r="H276" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -14219,22 +14300,16 @@
         <v>3</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
-      </c>
-      <c r="D277" t="s">
-        <v>23</v>
-      </c>
-      <c r="E277" t="s">
-        <v>160</v>
+        <v>79</v>
+      </c>
+      <c r="F277" t="s">
+        <v>127</v>
       </c>
       <c r="G277" t="s">
-        <v>129</v>
-      </c>
-      <c r="H277" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -14245,10 +14320,10 @@
         <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D278" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G278" t="s">
         <v>128</v>
@@ -14265,16 +14340,19 @@
         <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D279" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="E279" t="s">
+        <v>160</v>
       </c>
       <c r="G279" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H279" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -14285,19 +14363,16 @@
         <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D280" t="s">
-        <v>26</v>
-      </c>
-      <c r="E280" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
       <c r="G280" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H280" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -14308,10 +14383,10 @@
         <v>13</v>
       </c>
       <c r="C281" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G281" t="s">
         <v>128</v>
@@ -14328,13 +14403,13 @@
         <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D282" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E282" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G282" t="s">
         <v>129</v>
@@ -14351,19 +14426,16 @@
         <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D283" t="s">
-        <v>29</v>
-      </c>
-      <c r="E283" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="G283" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H283" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -14374,13 +14446,13 @@
         <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D284" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E284" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G284" t="s">
         <v>129</v>
@@ -14397,16 +14469,16 @@
         <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D285" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E285" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F285" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="G285" t="s">
         <v>128</v>
@@ -14420,16 +14492,16 @@
         <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D286" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="E286" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="F286" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="G286" t="s">
         <v>128</v>
@@ -14443,16 +14515,19 @@
         <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D287" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="E287" t="s">
+        <v>115</v>
+      </c>
+      <c r="F287" t="s">
+        <v>115</v>
       </c>
       <c r="G287" t="s">
         <v>128</v>
-      </c>
-      <c r="H287" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -14463,19 +14538,19 @@
         <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D288" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E288" t="s">
-        <v>160</v>
+        <v>182</v>
+      </c>
+      <c r="F288" t="s">
+        <v>118</v>
       </c>
       <c r="G288" t="s">
-        <v>129</v>
-      </c>
-      <c r="H288" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -14486,19 +14561,16 @@
         <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D289" t="s">
-        <v>35</v>
-      </c>
-      <c r="E289" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="G289" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H289" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -14509,13 +14581,13 @@
         <v>13</v>
       </c>
       <c r="C290" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D290" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G290" t="s">
         <v>129</v>
@@ -14532,16 +14604,16 @@
         <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D291" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E291" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="F291" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="G291" t="s">
         <v>128</v>
@@ -14555,22 +14627,19 @@
         <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D292" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E292" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="F292" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="G292" t="s">
-        <v>129</v>
-      </c>
-      <c r="H292" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -14581,16 +14650,19 @@
         <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D293" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="E293" t="s">
+        <v>116</v>
+      </c>
+      <c r="F293" t="s">
+        <v>116</v>
       </c>
       <c r="G293" t="s">
         <v>128</v>
-      </c>
-      <c r="H293" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -14601,19 +14673,22 @@
         <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D294" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E294" t="s">
-        <v>160</v>
+        <v>183</v>
+      </c>
+      <c r="F294" t="s">
+        <v>121</v>
       </c>
       <c r="G294" t="s">
         <v>129</v>
       </c>
       <c r="H294" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -14624,19 +14699,16 @@
         <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D295" t="s">
-        <v>41</v>
-      </c>
-      <c r="E295" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="G295" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H295" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -14647,13 +14719,13 @@
         <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D296" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E296" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G296" t="s">
         <v>129</v>
@@ -14670,22 +14742,19 @@
         <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D297" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E297" t="s">
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="F297" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G297" t="s">
-        <v>129</v>
-      </c>
-      <c r="H297" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -14696,22 +14765,19 @@
         <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D298" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E298" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="F298" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="G298" t="s">
-        <v>129</v>
-      </c>
-      <c r="H298" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -14722,16 +14788,22 @@
         <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D299" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="E299" t="s">
+        <v>184</v>
+      </c>
+      <c r="F299" t="s">
+        <v>117</v>
       </c>
       <c r="G299" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H299" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -14742,19 +14814,22 @@
         <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D300" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E300" t="s">
-        <v>160</v>
+        <v>185</v>
+      </c>
+      <c r="F300" t="s">
+        <v>123</v>
       </c>
       <c r="G300" t="s">
         <v>129</v>
       </c>
       <c r="H300" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -14765,19 +14840,16 @@
         <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D301" t="s">
-        <v>53</v>
-      </c>
-      <c r="E301" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G301" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H301" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -14788,13 +14860,13 @@
         <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D302" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E302" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="G302" t="s">
         <v>129</v>
@@ -14811,13 +14883,13 @@
         <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D303" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E303" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="G303" t="s">
         <v>129</v>
@@ -14834,19 +14906,19 @@
         <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D304" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E304" t="s">
-        <v>100</v>
-      </c>
-      <c r="F304" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G304" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="H304" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -14857,16 +14929,19 @@
         <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D305" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="E305" t="s">
+        <v>161</v>
       </c>
       <c r="G305" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H305" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -14877,16 +14952,19 @@
         <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D306" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="E306" t="s">
+        <v>102</v>
+      </c>
+      <c r="F306" t="s">
+        <v>102</v>
       </c>
       <c r="G306" t="s">
         <v>128</v>
-      </c>
-      <c r="H306" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -14897,10 +14975,10 @@
         <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D307" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="G307" t="s">
         <v>128</v>
@@ -14917,13 +14995,16 @@
         <v>13</v>
       </c>
       <c r="C308" t="s">
-        <v>64</v>
-      </c>
-      <c r="F308" t="s">
-        <v>117</v>
+        <v>58</v>
+      </c>
+      <c r="D308" t="s">
+        <v>58</v>
       </c>
       <c r="G308" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="H308" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -14934,13 +15015,16 @@
         <v>13</v>
       </c>
       <c r="C309" t="s">
-        <v>71</v>
-      </c>
-      <c r="F309" t="s">
-        <v>118</v>
+        <v>159</v>
+      </c>
+      <c r="D309" t="s">
+        <v>159</v>
       </c>
       <c r="G309" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="H309" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -14951,7 +15035,7 @@
         <v>13</v>
       </c>
       <c r="C310" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F310" t="s">
         <v>119</v>
@@ -14968,7 +15052,7 @@
         <v>13</v>
       </c>
       <c r="C311" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F311" t="s">
         <v>120</v>
@@ -14985,10 +15069,10 @@
         <v>13</v>
       </c>
       <c r="C312" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F312" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G312" t="s">
         <v>130</v>
@@ -15002,10 +15086,10 @@
         <v>13</v>
       </c>
       <c r="C313" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F313" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G313" t="s">
         <v>130</v>
@@ -15019,10 +15103,10 @@
         <v>13</v>
       </c>
       <c r="C314" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F314" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="G314" t="s">
         <v>130</v>
@@ -15036,7 +15120,7 @@
         <v>13</v>
       </c>
       <c r="C315" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F315" t="s">
         <v>122</v>
@@ -15053,7 +15137,7 @@
         <v>13</v>
       </c>
       <c r="C316" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F316" t="s">
         <v>123</v>
@@ -15087,10 +15171,10 @@
         <v>13</v>
       </c>
       <c r="C318" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F318" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="G318" t="s">
         <v>130</v>
@@ -15104,10 +15188,10 @@
         <v>13</v>
       </c>
       <c r="C319" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="F319" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G319" t="s">
         <v>130</v>
@@ -15121,10 +15205,10 @@
         <v>13</v>
       </c>
       <c r="C320" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="F320" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G320" t="s">
         <v>130</v>
@@ -15138,10 +15222,10 @@
         <v>13</v>
       </c>
       <c r="C321" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F321" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="G321" t="s">
         <v>130</v>
@@ -15152,19 +15236,16 @@
         <v>3</v>
       </c>
       <c r="B322" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C322" t="s">
-        <v>22</v>
-      </c>
-      <c r="D322" t="s">
-        <v>22</v>
+        <v>47</v>
+      </c>
+      <c r="F322" t="s">
+        <v>83</v>
       </c>
       <c r="G322" t="s">
-        <v>128</v>
-      </c>
-      <c r="H322" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -15172,19 +15253,16 @@
         <v>3</v>
       </c>
       <c r="B323" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C323" t="s">
-        <v>23</v>
-      </c>
-      <c r="D323" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="F323" t="s">
+        <v>83</v>
       </c>
       <c r="G323" t="s">
-        <v>128</v>
-      </c>
-      <c r="H323" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -15192,19 +15270,16 @@
         <v>3</v>
       </c>
       <c r="B324" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C324" t="s">
-        <v>24</v>
-      </c>
-      <c r="D324" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="F324" t="s">
+        <v>126</v>
       </c>
       <c r="G324" t="s">
-        <v>128</v>
-      </c>
-      <c r="H324" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -15212,19 +15287,16 @@
         <v>3</v>
       </c>
       <c r="B325" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C325" t="s">
-        <v>25</v>
-      </c>
-      <c r="D325" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F325" t="s">
+        <v>127</v>
       </c>
       <c r="G325" t="s">
-        <v>128</v>
-      </c>
-      <c r="H325" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -15235,19 +15307,16 @@
         <v>14</v>
       </c>
       <c r="C326" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D326" t="s">
-        <v>26</v>
-      </c>
-      <c r="E326" t="s">
-        <v>279</v>
+        <v>22</v>
       </c>
       <c r="G326" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H326" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -15258,10 +15327,10 @@
         <v>14</v>
       </c>
       <c r="C327" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D327" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G327" t="s">
         <v>128</v>
@@ -15278,10 +15347,10 @@
         <v>14</v>
       </c>
       <c r="C328" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D328" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G328" t="s">
         <v>128</v>
@@ -15298,19 +15367,16 @@
         <v>14</v>
       </c>
       <c r="C329" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>29</v>
-      </c>
-      <c r="E329" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G329" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H329" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -15321,13 +15387,13 @@
         <v>14</v>
       </c>
       <c r="C330" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D330" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E330" t="s">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="G330" t="s">
         <v>129</v>
@@ -15344,22 +15410,16 @@
         <v>14</v>
       </c>
       <c r="C331" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D331" t="s">
-        <v>31</v>
-      </c>
-      <c r="E331" t="s">
-        <v>280</v>
-      </c>
-      <c r="F331" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="G331" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H331" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -15370,19 +15430,16 @@
         <v>14</v>
       </c>
       <c r="C332" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D332" t="s">
-        <v>63</v>
-      </c>
-      <c r="E332" t="s">
-        <v>281</v>
-      </c>
-      <c r="F332" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="G332" t="s">
         <v>128</v>
+      </c>
+      <c r="H332" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -15393,16 +15450,19 @@
         <v>14</v>
       </c>
       <c r="C333" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D333" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="E333" t="s">
+        <v>83</v>
+      </c>
+      <c r="F333" t="s">
+        <v>83</v>
       </c>
       <c r="G333" t="s">
         <v>128</v>
-      </c>
-      <c r="H333" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -15413,16 +15473,19 @@
         <v>14</v>
       </c>
       <c r="C334" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D334" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="E334" t="s">
+        <v>83</v>
+      </c>
+      <c r="F334" t="s">
+        <v>83</v>
       </c>
       <c r="G334" t="s">
         <v>128</v>
-      </c>
-      <c r="H334" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -15433,19 +15496,22 @@
         <v>14</v>
       </c>
       <c r="C335" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D335" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E335" t="s">
-        <v>81</v>
+        <v>280</v>
+      </c>
+      <c r="F335" t="s">
+        <v>115</v>
       </c>
       <c r="G335" t="s">
         <v>129</v>
       </c>
       <c r="H335" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -15456,19 +15522,19 @@
         <v>14</v>
       </c>
       <c r="C336" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D336" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E336" t="s">
-        <v>81</v>
+        <v>281</v>
+      </c>
+      <c r="F336" t="s">
+        <v>118</v>
       </c>
       <c r="G336" t="s">
-        <v>129</v>
-      </c>
-      <c r="H336" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -15479,19 +15545,16 @@
         <v>14</v>
       </c>
       <c r="C337" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D337" t="s">
-        <v>37</v>
-      </c>
-      <c r="E337" t="s">
-        <v>282</v>
-      </c>
-      <c r="F337" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="G337" t="s">
         <v>128</v>
+      </c>
+      <c r="H337" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -15502,19 +15565,16 @@
         <v>14</v>
       </c>
       <c r="C338" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D338" t="s">
-        <v>65</v>
-      </c>
-      <c r="E338" t="s">
-        <v>283</v>
-      </c>
-      <c r="F338" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="G338" t="s">
         <v>128</v>
+      </c>
+      <c r="H338" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -15525,16 +15585,19 @@
         <v>14</v>
       </c>
       <c r="C339" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D339" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="E339" t="s">
+        <v>83</v>
+      </c>
+      <c r="F339" t="s">
+        <v>83</v>
       </c>
       <c r="G339" t="s">
         <v>128</v>
-      </c>
-      <c r="H339" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -15545,16 +15608,19 @@
         <v>14</v>
       </c>
       <c r="C340" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D340" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="E340" t="s">
+        <v>83</v>
+      </c>
+      <c r="F340" t="s">
+        <v>83</v>
       </c>
       <c r="G340" t="s">
         <v>128</v>
-      </c>
-      <c r="H340" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -15565,19 +15631,19 @@
         <v>14</v>
       </c>
       <c r="C341" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D341" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E341" t="s">
-        <v>81</v>
+        <v>282</v>
+      </c>
+      <c r="F341" t="s">
+        <v>116</v>
       </c>
       <c r="G341" t="s">
-        <v>129</v>
-      </c>
-      <c r="H341" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -15588,19 +15654,19 @@
         <v>14</v>
       </c>
       <c r="C342" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D342" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E342" t="s">
-        <v>81</v>
+        <v>283</v>
+      </c>
+      <c r="F342" t="s">
+        <v>121</v>
       </c>
       <c r="G342" t="s">
-        <v>129</v>
-      </c>
-      <c r="H342" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -15611,19 +15677,16 @@
         <v>14</v>
       </c>
       <c r="C343" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D343" t="s">
-        <v>43</v>
-      </c>
-      <c r="E343" t="s">
-        <v>284</v>
-      </c>
-      <c r="F343" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="G343" t="s">
         <v>128</v>
+      </c>
+      <c r="H343" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -15634,19 +15697,16 @@
         <v>14</v>
       </c>
       <c r="C344" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D344" t="s">
-        <v>69</v>
-      </c>
-      <c r="E344" t="s">
-        <v>122</v>
-      </c>
-      <c r="F344" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="G344" t="s">
         <v>128</v>
+      </c>
+      <c r="H344" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -15657,16 +15717,19 @@
         <v>14</v>
       </c>
       <c r="C345" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D345" t="s">
-        <v>51</v>
+        <v>41</v>
+      </c>
+      <c r="E345" t="s">
+        <v>83</v>
+      </c>
+      <c r="F345" t="s">
+        <v>83</v>
       </c>
       <c r="G345" t="s">
         <v>128</v>
-      </c>
-      <c r="H345" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -15677,16 +15740,19 @@
         <v>14</v>
       </c>
       <c r="C346" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D346" t="s">
-        <v>52</v>
+        <v>42</v>
+      </c>
+      <c r="E346" t="s">
+        <v>83</v>
+      </c>
+      <c r="F346" t="s">
+        <v>83</v>
       </c>
       <c r="G346" t="s">
         <v>128</v>
-      </c>
-      <c r="H346" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -15697,19 +15763,19 @@
         <v>14</v>
       </c>
       <c r="C347" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D347" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E347" t="s">
-        <v>81</v>
+        <v>284</v>
+      </c>
+      <c r="F347" t="s">
+        <v>117</v>
       </c>
       <c r="G347" t="s">
-        <v>129</v>
-      </c>
-      <c r="H347" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -15720,19 +15786,19 @@
         <v>14</v>
       </c>
       <c r="C348" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D348" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E348" t="s">
-        <v>89</v>
+        <v>123</v>
+      </c>
+      <c r="F348" t="s">
+        <v>123</v>
       </c>
       <c r="G348" t="s">
-        <v>129</v>
-      </c>
-      <c r="H348" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -15743,19 +15809,16 @@
         <v>14</v>
       </c>
       <c r="C349" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D349" t="s">
-        <v>55</v>
-      </c>
-      <c r="E349" t="s">
-        <v>279</v>
+        <v>51</v>
       </c>
       <c r="G349" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H349" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -15766,19 +15829,16 @@
         <v>14</v>
       </c>
       <c r="C350" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D350" t="s">
-        <v>56</v>
-      </c>
-      <c r="E350" t="s">
-        <v>100</v>
-      </c>
-      <c r="F350" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="G350" t="s">
         <v>128</v>
+      </c>
+      <c r="H350" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -15789,22 +15849,19 @@
         <v>14</v>
       </c>
       <c r="C351" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D351" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E351" t="s">
-        <v>285</v>
-      </c>
-      <c r="F351" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="G351" t="s">
         <v>129</v>
       </c>
       <c r="H351" t="s">
-        <v>288</v>
+        <v>132</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -15815,13 +15872,13 @@
         <v>14</v>
       </c>
       <c r="C352" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D352" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E352" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G352" t="s">
         <v>129</v>
@@ -15838,13 +15895,13 @@
         <v>14</v>
       </c>
       <c r="C353" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D353" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E353" t="s">
-        <v>101</v>
+        <v>279</v>
       </c>
       <c r="G353" t="s">
         <v>129</v>
@@ -15861,16 +15918,19 @@
         <v>14</v>
       </c>
       <c r="C354" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D354" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="E354" t="s">
+        <v>102</v>
+      </c>
+      <c r="F354" t="s">
+        <v>102</v>
       </c>
       <c r="G354" t="s">
         <v>128</v>
-      </c>
-      <c r="H354" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -15881,16 +15941,22 @@
         <v>14</v>
       </c>
       <c r="C355" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D355" t="s">
-        <v>61</v>
+        <v>79</v>
+      </c>
+      <c r="E355" t="s">
+        <v>285</v>
+      </c>
+      <c r="F355" t="s">
+        <v>127</v>
       </c>
       <c r="G355" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H355" t="s">
-        <v>131</v>
+        <v>288</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -15901,13 +15967,13 @@
         <v>14</v>
       </c>
       <c r="C356" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D356" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E356" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="G356" t="s">
         <v>129</v>
@@ -15924,16 +15990,19 @@
         <v>14</v>
       </c>
       <c r="C357" t="s">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="D357" t="s">
-        <v>252</v>
+        <v>58</v>
+      </c>
+      <c r="E357" t="s">
+        <v>103</v>
       </c>
       <c r="G357" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H357" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -15944,10 +16013,10 @@
         <v>14</v>
       </c>
       <c r="C358" t="s">
-        <v>253</v>
+        <v>60</v>
       </c>
       <c r="D358" t="s">
-        <v>253</v>
+        <v>60</v>
       </c>
       <c r="G358" t="s">
         <v>128</v>
@@ -15964,10 +16033,10 @@
         <v>14</v>
       </c>
       <c r="C359" t="s">
-        <v>254</v>
+        <v>61</v>
       </c>
       <c r="D359" t="s">
-        <v>254</v>
+        <v>61</v>
       </c>
       <c r="G359" t="s">
         <v>128</v>
@@ -15984,13 +16053,19 @@
         <v>14</v>
       </c>
       <c r="C360" t="s">
-        <v>64</v>
-      </c>
-      <c r="F360" t="s">
-        <v>117</v>
+        <v>62</v>
+      </c>
+      <c r="D360" t="s">
+        <v>62</v>
+      </c>
+      <c r="E360" t="s">
+        <v>181</v>
       </c>
       <c r="G360" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="H360" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -16001,13 +16076,16 @@
         <v>14</v>
       </c>
       <c r="C361" t="s">
-        <v>71</v>
-      </c>
-      <c r="F361" t="s">
-        <v>118</v>
+        <v>252</v>
+      </c>
+      <c r="D361" t="s">
+        <v>252</v>
       </c>
       <c r="G361" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="H361" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -16018,13 +16096,16 @@
         <v>14</v>
       </c>
       <c r="C362" t="s">
-        <v>72</v>
-      </c>
-      <c r="F362" t="s">
-        <v>119</v>
+        <v>253</v>
+      </c>
+      <c r="D362" t="s">
+        <v>253</v>
       </c>
       <c r="G362" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="H362" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -16035,13 +16116,16 @@
         <v>14</v>
       </c>
       <c r="C363" t="s">
-        <v>31</v>
-      </c>
-      <c r="F363" t="s">
-        <v>113</v>
+        <v>254</v>
+      </c>
+      <c r="D363" t="s">
+        <v>254</v>
       </c>
       <c r="G363" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="H363" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -16052,10 +16136,10 @@
         <v>14</v>
       </c>
       <c r="C364" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F364" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G364" t="s">
         <v>130</v>
@@ -16069,10 +16153,10 @@
         <v>14</v>
       </c>
       <c r="C365" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F365" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G365" t="s">
         <v>130</v>
@@ -16086,10 +16170,10 @@
         <v>14</v>
       </c>
       <c r="C366" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="F366" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G366" t="s">
         <v>130</v>
@@ -16103,10 +16187,10 @@
         <v>14</v>
       </c>
       <c r="C367" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F367" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G367" t="s">
         <v>130</v>
@@ -16120,10 +16204,10 @@
         <v>14</v>
       </c>
       <c r="C368" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F368" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G368" t="s">
         <v>130</v>
@@ -16137,10 +16221,10 @@
         <v>14</v>
       </c>
       <c r="C369" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F369" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G369" t="s">
         <v>130</v>
@@ -16154,10 +16238,10 @@
         <v>14</v>
       </c>
       <c r="C370" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F370" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G370" t="s">
         <v>130</v>
@@ -16171,12 +16255,114 @@
         <v>14</v>
       </c>
       <c r="C371" t="s">
+        <v>76</v>
+      </c>
+      <c r="F371" t="s">
+        <v>91</v>
+      </c>
+      <c r="G371" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372">
+        <v>3</v>
+      </c>
+      <c r="B372" t="s">
+        <v>14</v>
+      </c>
+      <c r="C372" t="s">
         <v>77</v>
       </c>
-      <c r="F371" t="s">
+      <c r="F372" t="s">
+        <v>125</v>
+      </c>
+      <c r="G372" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373">
+        <v>3</v>
+      </c>
+      <c r="B373" t="s">
+        <v>14</v>
+      </c>
+      <c r="C373" t="s">
+        <v>78</v>
+      </c>
+      <c r="F373" t="s">
+        <v>91</v>
+      </c>
+      <c r="G373" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374">
+        <v>3</v>
+      </c>
+      <c r="B374" t="s">
+        <v>14</v>
+      </c>
+      <c r="C374" t="s">
+        <v>47</v>
+      </c>
+      <c r="F374" t="s">
+        <v>83</v>
+      </c>
+      <c r="G374" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375">
+        <v>3</v>
+      </c>
+      <c r="B375" t="s">
+        <v>14</v>
+      </c>
+      <c r="C375" t="s">
+        <v>48</v>
+      </c>
+      <c r="F375" t="s">
+        <v>83</v>
+      </c>
+      <c r="G375" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376">
+        <v>3</v>
+      </c>
+      <c r="B376" t="s">
+        <v>14</v>
+      </c>
+      <c r="C376" t="s">
+        <v>49</v>
+      </c>
+      <c r="F376" t="s">
+        <v>126</v>
+      </c>
+      <c r="G376" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377">
+        <v>3</v>
+      </c>
+      <c r="B377" t="s">
+        <v>14</v>
+      </c>
+      <c r="C377" t="s">
+        <v>79</v>
+      </c>
+      <c r="F377" t="s">
         <v>127</v>
       </c>
-      <c r="G371" t="s">
+      <c r="G377" t="s">
         <v>130</v>
       </c>
     </row>

--- a/data/output/rda/runs/v9-narrative/evaluation_results.xlsx
+++ b/data/output/rda/runs/v9-narrative/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="123">
   <si>
     <t>fields in reference</t>
   </si>
@@ -194,9 +194,6 @@
     <t>dmp.dataset[0].distribution[0].host.title</t>
   </si>
   <si>
-    <t>dmp.dataset[0].metadata[0].description</t>
-  </si>
-  <si>
     <t>dmp.dataset[1].description</t>
   </si>
   <si>
@@ -284,10 +281,10 @@
     <t>servers at the Rehabilitation Institute of Chicago</t>
   </si>
   <si>
+    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
+  </si>
+  <si>
     <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
-  </si>
-  <si>
-    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
   </si>
   <si>
     <t>The code needed to generate all published results will be documented clearly.</t>
@@ -793,7 +790,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>34</v>
@@ -805,25 +802,25 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>0.706</v>
       </c>
       <c r="H2">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>0.498</v>
+        <v>0.511</v>
       </c>
       <c r="J2">
-        <v>0.48</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="K2">
-        <v>0.2</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="L2">
-        <v>0.32</v>
+        <v>0.3061224489795918</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -831,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>32</v>
@@ -843,25 +840,25 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>0.625</v>
       </c>
       <c r="H3">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
-        <v>0.476</v>
+        <v>0.488</v>
       </c>
       <c r="J3">
-        <v>0.4166666666666667</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="K3">
-        <v>0.25</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="L3">
-        <v>0.3333333333333333</v>
+        <v>0.3191489361702128</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -869,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -881,25 +878,25 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>0.763</v>
       </c>
       <c r="H4">
-        <v>0.462</v>
+        <v>0.48</v>
       </c>
       <c r="I4">
-        <v>0.575</v>
+        <v>0.589</v>
       </c>
       <c r="J4">
-        <v>0.5576923076923077</v>
+        <v>0.5686274509803921</v>
       </c>
       <c r="K4">
-        <v>0.1730769230769231</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="L4">
-        <v>0.2692307692307692</v>
+        <v>0.2549019607843137</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -946,10 +943,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -963,10 +960,10 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -980,10 +977,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -997,10 +994,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1014,13 +1011,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1034,10 +1031,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1051,10 +1048,10 @@
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1068,13 +1065,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1088,13 +1085,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1108,13 +1105,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1128,13 +1125,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1148,10 +1145,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1165,10 +1162,10 @@
         <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1182,13 +1179,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1202,13 +1199,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1222,13 +1219,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1242,13 +1239,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1262,10 +1259,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1279,10 +1276,10 @@
         <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1296,13 +1293,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1316,13 +1313,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1336,13 +1333,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1356,13 +1353,13 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1376,10 +1373,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1393,10 +1390,10 @@
         <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1410,13 +1407,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1430,13 +1427,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1450,13 +1447,13 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1470,13 +1467,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1490,13 +1487,13 @@
         <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1510,13 +1507,13 @@
         <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1530,10 +1527,10 @@
         <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1547,10 +1544,10 @@
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1564,13 +1561,13 @@
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1581,10 +1578,10 @@
         <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1595,10 +1592,10 @@
         <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1609,10 +1606,10 @@
         <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1623,10 +1620,10 @@
         <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1637,10 +1634,10 @@
         <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1651,10 +1648,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1668,7 +1665,7 @@
         <v>90</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1682,7 +1679,7 @@
         <v>91</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1693,10 +1690,10 @@
         <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1707,10 +1704,10 @@
         <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1721,10 +1718,10 @@
         <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1735,10 +1732,10 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1749,10 +1746,10 @@
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1763,10 +1760,10 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1780,21 +1777,7 @@
         <v>94</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1804,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1841,10 +1824,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1858,13 +1841,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1878,10 +1861,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1895,10 +1878,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1912,13 +1895,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1932,10 +1915,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1949,13 +1932,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1969,13 +1952,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1989,13 +1972,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2009,13 +1992,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2029,13 +2012,13 @@
         <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2049,10 +2032,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2066,13 +2049,13 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2086,13 +2069,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2106,13 +2089,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2126,13 +2109,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2140,22 +2123,22 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2169,10 +2152,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2186,13 +2169,13 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2206,13 +2189,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2226,13 +2209,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2246,16 +2229,16 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2263,22 +2246,22 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2292,10 +2275,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2309,13 +2292,13 @@
         <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2329,13 +2312,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2349,13 +2332,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2369,13 +2352,13 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2389,13 +2372,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2409,10 +2392,10 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2426,10 +2409,10 @@
         <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2437,16 +2420,16 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2457,10 +2440,10 @@
         <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2471,10 +2454,10 @@
         <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2485,10 +2468,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2499,10 +2482,10 @@
         <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2513,10 +2496,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2530,7 +2513,7 @@
         <v>90</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2544,7 +2527,7 @@
         <v>91</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2555,10 +2538,10 @@
         <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2566,13 +2549,13 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2580,13 +2563,13 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2597,10 +2580,10 @@
         <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2611,10 +2594,10 @@
         <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2625,10 +2608,10 @@
         <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2639,10 +2622,10 @@
         <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2656,21 +2639,7 @@
         <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>3</v>
-      </c>
-      <c r="B49" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" t="s">
-        <v>95</v>
-      </c>
-      <c r="F49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2717,10 +2686,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2734,10 +2703,10 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2751,10 +2720,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2768,10 +2737,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2785,13 +2754,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2805,10 +2774,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2822,10 +2791,10 @@
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2839,13 +2808,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2859,13 +2828,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2879,16 +2848,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2902,13 +2871,13 @@
         <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2922,10 +2891,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2939,10 +2908,10 @@
         <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2956,13 +2925,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2976,13 +2945,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2996,13 +2965,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3010,19 +2979,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3036,10 +3005,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3053,10 +3022,10 @@
         <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3070,13 +3039,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3090,13 +3059,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3110,13 +3079,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3124,19 +3093,19 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3150,10 +3119,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3167,10 +3136,10 @@
         <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3184,13 +3153,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3204,13 +3173,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3224,13 +3193,13 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3244,13 +3213,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3258,22 +3227,22 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3287,13 +3256,13 @@
         <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3307,13 +3276,13 @@
         <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3327,10 +3296,10 @@
         <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3344,10 +3313,10 @@
         <v>54</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3361,13 +3330,13 @@
         <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3375,16 +3344,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3392,16 +3361,16 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3409,16 +3378,16 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3429,10 +3398,10 @@
         <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3440,13 +3409,13 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3454,13 +3423,13 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3471,10 +3440,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3485,10 +3454,10 @@
         <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3496,13 +3465,13 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3513,10 +3482,10 @@
         <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3527,10 +3496,10 @@
         <v>65</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3541,10 +3510,10 @@
         <v>66</v>
       </c>
       <c r="E48" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3555,10 +3524,10 @@
         <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3569,10 +3538,10 @@
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3583,10 +3552,10 @@
         <v>69</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3600,21 +3569,7 @@
         <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" t="s">
-        <v>95</v>
-      </c>
-      <c r="F53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3624,7 +3579,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3667,10 +3622,10 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3687,10 +3642,10 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3707,10 +3662,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3727,10 +3682,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3747,13 +3702,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3770,10 +3725,10 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3790,10 +3745,10 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3810,13 +3765,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3833,13 +3788,13 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3856,13 +3811,13 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3879,13 +3834,13 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3902,10 +3857,10 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3922,10 +3877,10 @@
         <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3942,13 +3897,13 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3965,13 +3920,13 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3988,13 +3943,13 @@
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4011,13 +3966,13 @@
         <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4034,10 +3989,10 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4054,10 +4009,10 @@
         <v>40</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4074,13 +4029,13 @@
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4097,13 +4052,13 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4120,13 +4075,13 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4143,13 +4098,13 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4166,10 +4121,10 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4186,10 +4141,10 @@
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4206,13 +4161,13 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4229,13 +4184,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4252,13 +4207,13 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4275,13 +4230,13 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4298,13 +4253,13 @@
         <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4321,13 +4276,13 @@
         <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -4344,10 +4299,10 @@
         <v>53</v>
       </c>
       <c r="G33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4364,10 +4319,10 @@
         <v>54</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4384,13 +4339,13 @@
         <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4404,10 +4359,10 @@
         <v>56</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4421,10 +4376,10 @@
         <v>57</v>
       </c>
       <c r="F37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4438,10 +4393,10 @@
         <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4455,10 +4410,10 @@
         <v>59</v>
       </c>
       <c r="F39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4472,10 +4427,10 @@
         <v>60</v>
       </c>
       <c r="F40" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4489,10 +4444,10 @@
         <v>61</v>
       </c>
       <c r="F41" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -4509,7 +4464,7 @@
         <v>90</v>
       </c>
       <c r="G42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4526,7 +4481,7 @@
         <v>91</v>
       </c>
       <c r="G43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4540,10 +4495,10 @@
         <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -4557,10 +4512,10 @@
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4574,10 +4529,10 @@
         <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4591,10 +4546,10 @@
         <v>67</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4608,10 +4563,10 @@
         <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4625,10 +4580,10 @@
         <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4645,7 +4600,7 @@
         <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4653,15 +4608,18 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
-      </c>
-      <c r="F51" t="s">
-        <v>95</v>
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
       </c>
       <c r="G51" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4673,10 +4631,13 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="E52" t="s">
+        <v>101</v>
       </c>
       <c r="G52" t="s">
         <v>96</v>
@@ -4693,19 +4654,16 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -4716,16 +4674,16 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -4736,10 +4694,13 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="E55" t="s">
+        <v>102</v>
       </c>
       <c r="G55" t="s">
         <v>96</v>
@@ -4756,19 +4717,16 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -4779,10 +4737,13 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E57" t="s">
+        <v>101</v>
       </c>
       <c r="G57" t="s">
         <v>96</v>
@@ -4799,19 +4760,19 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>102</v>
+        <v>72</v>
+      </c>
+      <c r="F58" t="s">
+        <v>72</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
-      </c>
-      <c r="H58" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -4822,19 +4783,19 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -4845,19 +4806,19 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F60" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -4868,19 +4829,19 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="E61" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -4891,19 +4852,16 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
-      </c>
-      <c r="E62" t="s">
-        <v>104</v>
-      </c>
-      <c r="F62" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G62" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H62" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -4914,10 +4872,13 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E63" t="s">
+        <v>101</v>
       </c>
       <c r="G63" t="s">
         <v>96</v>
@@ -4934,19 +4895,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s">
-        <v>102</v>
+        <v>72</v>
+      </c>
+      <c r="F64" t="s">
+        <v>72</v>
       </c>
       <c r="G64" t="s">
-        <v>97</v>
-      </c>
-      <c r="H64" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -4957,19 +4918,19 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -4980,19 +4941,19 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E66" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5003,20 +4964,23 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E67" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="F67" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s">
         <v>96</v>
       </c>
+      <c r="H67" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
@@ -5026,22 +4990,16 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
-      </c>
-      <c r="E68" t="s">
-        <v>105</v>
-      </c>
-      <c r="F68" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5052,10 +5010,13 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>101</v>
       </c>
       <c r="G69" t="s">
         <v>96</v>
@@ -5072,19 +5033,19 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>72</v>
+      </c>
+      <c r="F70" t="s">
+        <v>72</v>
       </c>
       <c r="G70" t="s">
-        <v>97</v>
-      </c>
-      <c r="H70" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5095,19 +5056,19 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5118,20 +5079,23 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E72" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G72" t="s">
         <v>96</v>
       </c>
+      <c r="H72" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
@@ -5141,19 +5105,19 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E73" t="s">
         <v>106</v>
       </c>
       <c r="F73" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H73" t="s">
         <v>109</v>
@@ -5167,22 +5131,16 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
-      </c>
-      <c r="E74" t="s">
-        <v>107</v>
-      </c>
-      <c r="F74" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="G74" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5193,10 +5151,13 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D75" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="E75" t="s">
+        <v>101</v>
       </c>
       <c r="G75" t="s">
         <v>96</v>
@@ -5213,19 +5174,19 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E76" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5236,19 +5197,19 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E77" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5259,19 +5220,19 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5282,19 +5243,19 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E79" t="s">
-        <v>103</v>
+        <v>79</v>
+      </c>
+      <c r="F79" t="s">
+        <v>79</v>
       </c>
       <c r="G79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H79" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -5305,19 +5266,16 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E80" t="s">
-        <v>80</v>
-      </c>
-      <c r="F80" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G80" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H80" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -5328,16 +5286,16 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D81" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -5348,16 +5306,16 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -5368,16 +5326,13 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
-      </c>
-      <c r="D83" t="s">
-        <v>101</v>
+        <v>57</v>
+      </c>
+      <c r="F83" t="s">
+        <v>86</v>
       </c>
       <c r="G83" t="s">
-        <v>96</v>
-      </c>
-      <c r="H83" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -5388,13 +5343,13 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F84" t="s">
         <v>87</v>
       </c>
       <c r="G84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -5405,13 +5360,13 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F85" t="s">
         <v>88</v>
       </c>
       <c r="G85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -5422,13 +5377,13 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F86" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -5439,13 +5394,13 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -5456,13 +5411,13 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F88" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -5473,13 +5428,13 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G89" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -5490,13 +5445,13 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F90" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -5507,13 +5462,13 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F91" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -5527,10 +5482,10 @@
         <v>65</v>
       </c>
       <c r="F92" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -5541,13 +5496,13 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F93" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -5558,13 +5513,13 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F94" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="G94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -5575,13 +5530,13 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F95" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -5592,13 +5547,13 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F96" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="G96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -5609,13 +5564,13 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F97" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -5623,15 +5578,18 @@
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
-      </c>
-      <c r="F98" t="s">
-        <v>94</v>
+        <v>22</v>
+      </c>
+      <c r="D98" t="s">
+        <v>22</v>
       </c>
       <c r="G98" t="s">
+        <v>95</v>
+      </c>
+      <c r="H98" t="s">
         <v>98</v>
       </c>
     </row>
@@ -5640,15 +5598,18 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>71</v>
-      </c>
-      <c r="F99" t="s">
-        <v>95</v>
+        <v>23</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
       </c>
       <c r="G99" t="s">
+        <v>95</v>
+      </c>
+      <c r="H99" t="s">
         <v>98</v>
       </c>
     </row>
@@ -5660,16 +5621,16 @@
         <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -5680,16 +5641,16 @@
         <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -5700,10 +5661,13 @@
         <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="E102" t="s">
+        <v>113</v>
       </c>
       <c r="G102" t="s">
         <v>96</v>
@@ -5720,16 +5684,16 @@
         <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -5740,19 +5704,16 @@
         <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D104" t="s">
-        <v>26</v>
-      </c>
-      <c r="E104" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -5763,16 +5724,19 @@
         <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="E105" t="s">
+        <v>72</v>
+      </c>
+      <c r="F105" t="s">
+        <v>72</v>
       </c>
       <c r="G105" t="s">
-        <v>96</v>
-      </c>
-      <c r="H105" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -5783,16 +5747,19 @@
         <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D106" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E106" t="s">
+        <v>72</v>
+      </c>
+      <c r="F106" t="s">
+        <v>72</v>
       </c>
       <c r="G106" t="s">
-        <v>96</v>
-      </c>
-      <c r="H106" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -5803,20 +5770,23 @@
         <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E107" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="F107" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G107" t="s">
         <v>96</v>
       </c>
+      <c r="H107" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
@@ -5826,19 +5796,19 @@
         <v>14</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D108" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E108" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="F108" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -5849,22 +5819,16 @@
         <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
-      </c>
-      <c r="E109" t="s">
-        <v>115</v>
-      </c>
-      <c r="F109" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G109" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H109" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -5875,19 +5839,16 @@
         <v>14</v>
       </c>
       <c r="C110" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D110" t="s">
-        <v>56</v>
-      </c>
-      <c r="E110" t="s">
-        <v>116</v>
-      </c>
-      <c r="F110" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="G110" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H110" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -5898,16 +5859,19 @@
         <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>72</v>
+      </c>
+      <c r="F111" t="s">
+        <v>72</v>
       </c>
       <c r="G111" t="s">
-        <v>96</v>
-      </c>
-      <c r="H111" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -5918,16 +5882,19 @@
         <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E112" t="s">
+        <v>72</v>
+      </c>
+      <c r="F112" t="s">
+        <v>72</v>
       </c>
       <c r="G112" t="s">
-        <v>96</v>
-      </c>
-      <c r="H112" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -5938,19 +5905,19 @@
         <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D113" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E113" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="F113" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G113" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -5961,19 +5928,19 @@
         <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D114" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E114" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="F114" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G114" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -5984,19 +5951,16 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D115" t="s">
-        <v>37</v>
-      </c>
-      <c r="E115" t="s">
-        <v>117</v>
-      </c>
-      <c r="F115" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="G115" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H115" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6007,19 +5971,16 @@
         <v>14</v>
       </c>
       <c r="C116" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
-      </c>
-      <c r="E116" t="s">
-        <v>118</v>
-      </c>
-      <c r="F116" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="G116" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H116" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6030,16 +5991,19 @@
         <v>14</v>
       </c>
       <c r="C117" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D117" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="E117" t="s">
+        <v>72</v>
+      </c>
+      <c r="F117" t="s">
+        <v>72</v>
       </c>
       <c r="G117" t="s">
-        <v>96</v>
-      </c>
-      <c r="H117" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6050,16 +6014,19 @@
         <v>14</v>
       </c>
       <c r="C118" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D118" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="E118" t="s">
+        <v>72</v>
+      </c>
+      <c r="F118" t="s">
+        <v>72</v>
       </c>
       <c r="G118" t="s">
-        <v>96</v>
-      </c>
-      <c r="H118" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6070,19 +6037,19 @@
         <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D119" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E119" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="F119" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6093,19 +6060,19 @@
         <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D120" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E120" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F120" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G120" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6116,19 +6083,16 @@
         <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D121" t="s">
-        <v>43</v>
-      </c>
-      <c r="E121" t="s">
-        <v>119</v>
-      </c>
-      <c r="F121" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="G121" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H121" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6139,19 +6103,16 @@
         <v>14</v>
       </c>
       <c r="C122" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D122" t="s">
-        <v>63</v>
-      </c>
-      <c r="E122" t="s">
-        <v>91</v>
-      </c>
-      <c r="F122" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="G122" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="H122" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6162,10 +6123,13 @@
         <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D123" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="E123" t="s">
+        <v>72</v>
       </c>
       <c r="G123" t="s">
         <v>96</v>
@@ -6182,10 +6146,13 @@
         <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D124" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="E124" t="s">
+        <v>78</v>
       </c>
       <c r="G124" t="s">
         <v>96</v>
@@ -6202,19 +6169,19 @@
         <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E125" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H125" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6225,19 +6192,19 @@
         <v>14</v>
       </c>
       <c r="C126" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D126" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E126" t="s">
         <v>79</v>
       </c>
+      <c r="F126" t="s">
+        <v>79</v>
+      </c>
       <c r="G126" t="s">
-        <v>97</v>
-      </c>
-      <c r="H126" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6248,19 +6215,22 @@
         <v>14</v>
       </c>
       <c r="C127" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D127" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E127" t="s">
-        <v>114</v>
+        <v>119</v>
+      </c>
+      <c r="F127" t="s">
+        <v>94</v>
       </c>
       <c r="G127" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H127" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6271,20 +6241,20 @@
         <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D128" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E128" t="s">
-        <v>80</v>
-      </c>
-      <c r="F128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
         <v>96</v>
       </c>
+      <c r="H128" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
@@ -6294,22 +6264,19 @@
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E129" t="s">
-        <v>120</v>
-      </c>
-      <c r="F129" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G129" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H129" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -6320,19 +6287,16 @@
         <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D130" t="s">
-        <v>51</v>
-      </c>
-      <c r="E130" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="G130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H130" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -6343,19 +6307,16 @@
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D131" t="s">
-        <v>52</v>
-      </c>
-      <c r="E131" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G131" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H131" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -6366,10 +6327,13 @@
         <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="E132" t="s">
+        <v>120</v>
       </c>
       <c r="G132" t="s">
         <v>96</v>
@@ -6386,16 +6350,16 @@
         <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="D133" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="G133" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H133" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -6406,19 +6370,16 @@
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="D134" t="s">
-        <v>55</v>
-      </c>
-      <c r="E134" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G134" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H134" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -6429,16 +6390,16 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D135" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G135" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H135" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -6449,16 +6410,13 @@
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>112</v>
-      </c>
-      <c r="D136" t="s">
-        <v>112</v>
+        <v>57</v>
+      </c>
+      <c r="F136" t="s">
+        <v>86</v>
       </c>
       <c r="G136" t="s">
-        <v>96</v>
-      </c>
-      <c r="H136" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -6469,16 +6427,13 @@
         <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>113</v>
-      </c>
-      <c r="D137" t="s">
-        <v>113</v>
+        <v>31</v>
+      </c>
+      <c r="F137" t="s">
+        <v>82</v>
       </c>
       <c r="G137" t="s">
-        <v>96</v>
-      </c>
-      <c r="H137" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -6489,13 +6444,13 @@
         <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F138" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G138" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -6506,13 +6461,13 @@
         <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F139" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G139" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -6523,13 +6478,13 @@
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F140" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G140" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -6540,13 +6495,13 @@
         <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F141" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G141" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -6557,13 +6512,13 @@
         <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G142" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -6574,13 +6529,13 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F143" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G143" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -6591,13 +6546,13 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F144" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G144" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -6608,13 +6563,13 @@
         <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F145" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G145" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -6625,13 +6580,13 @@
         <v>14</v>
       </c>
       <c r="C146" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F146" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="G146" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -6642,13 +6597,13 @@
         <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F147" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G147" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -6659,64 +6614,13 @@
         <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F148" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="G148" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149">
-        <v>3</v>
-      </c>
-      <c r="B149" t="s">
-        <v>14</v>
-      </c>
-      <c r="C149" t="s">
-        <v>69</v>
-      </c>
-      <c r="F149" t="s">
-        <v>73</v>
-      </c>
-      <c r="G149" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150">
-        <v>3</v>
-      </c>
-      <c r="B150" t="s">
-        <v>14</v>
-      </c>
-      <c r="C150" t="s">
-        <v>70</v>
-      </c>
-      <c r="F150" t="s">
-        <v>94</v>
-      </c>
-      <c r="G150" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151">
-        <v>3</v>
-      </c>
-      <c r="B151" t="s">
-        <v>14</v>
-      </c>
-      <c r="C151" t="s">
-        <v>71</v>
-      </c>
-      <c r="F151" t="s">
-        <v>95</v>
-      </c>
-      <c r="G151" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
